--- a/data/trans_dic/P79$hipoteca_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79$hipoteca_2023-Estudios-trans_dic.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,65</t>
+          <t>0,08; 0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,51</t>
+          <t>0,05; 0,52</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,52</t>
+          <t>0,77; 1,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,21</t>
+          <t>0,59; 1,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,26</t>
+          <t>0,78; 1,46</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,42</t>
+          <t>0,48; 2,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,49</t>
+          <t>0,24; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,49</t>
+          <t>0,51; 1,56</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,31</t>
+          <t>0,71; 1,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,92</t>
+          <t>0,49; 0,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,04</t>
+          <t>0,68; 1,1</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>964</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>0; 5750</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>554; 4679</t>
+          <t>609; 4658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>617; 6119</t>
+          <t>638; 6968</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39414</t>
+          <t>44580</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14030; 33729</t>
+          <t>16548; 38022</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10442; 25434</t>
+          <t>12448; 27449</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28391; 54534</t>
+          <t>33272; 61955</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>12763</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3854; 15535</t>
+          <t>3398; 16104</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1572; 9641</t>
+          <t>1686; 10090</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6191; 19149</t>
+          <t>7272; 22220</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19240; 44052</t>
+          <t>24202; 48573</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15287; 31890</t>
+          <t>17645; 35412</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41773; 71047</t>
+          <t>47791; 77308</t>
         </is>
       </c>
     </row>
